--- a/docs/MML_Sales_API_Documentation.xlsx
+++ b/docs/MML_Sales_API_Documentation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="226">
   <si>
     <t>MML Sales CRM — API Documentation (Client Share)</t>
   </si>
@@ -1045,13 +1045,370 @@
     <t>PersonalAssistantCard Ask anything (message state)</t>
   </si>
   <si>
+    <t>PAGE 4: Deal Detail — Profile Create / Intake (P2) — Files: IntakeFormTab.jsx + intake/intakeFormData.js</t>
+  </si>
+  <si>
+    <t>Default tab when stageId=P2 (STAGE_TO_TAB). Two FE views (toggle is FE-only): Fill the form + Client record. Booklet sections (FE labels): personal, education, residency, family, siblings, match, essential, medical, declaration, communication, casesheet. Field keys = intakeFormData.js (e.g. firstName, mobile, courses[]). Client-record / personal saves require OTP (send → verify → commit). Move P2→P3 uses existing PATCH .../stage.</t>
+  </si>
+  <si>
+    <t>▶ GET Requests — Intake / Profile Create (P2)</t>
+  </si>
+  <si>
+    <t>Get Intake Form (full booklet)</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/intake</t>
+  </si>
+  <si>
+    <t>DYNAMIC intake state for both Fill form + Client record. values = flat map of field keys from SECTION_BLOCKS; chips holds upload chip lists (e.g. aadhaarFiles). Progress numbers for Form filled card / section sidebar. Schema labels stay on FE (SECTIONS_META).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "p2-1",
+    "stageId": "P2",
+    "personalUnlocked": false,
+    "overallFilledFields": 145,
+    "overallTotalFields": 270,
+    "overallPercent": 54,
+    "sections": [
+      {
+        "key": "personal",
+        "filled": 28,
+        "total": 40,
+        "percent": 70
+      },
+      {
+        "key": "education",
+        "filled": 12,
+        "total": 25,
+        "percent": 48
+      }
+    ],
+    "values": {
+      "gender": "Female",
+      "firstName": "Priya",
+      "middleName": "",
+      "lastName": "Raheja",
+      "clientType": "Exclusive",
+      "profileStatus": "Under review",
+      "maritalStatus": "Never married",
+      "lookingFor": "Groom",
+      "enquiryBy": "Parent",
+      "panNo": "AHXPR••••K",
+      "aadhaarNo": "•••• •••• 4417",
+      "mobile": "98••• ••164",
+      "alternateContact": "",
+      "email": "priya.raheja@gmail.com",
+      "dob": "14 Jul 1995",
+      "timeOfBirth": "04:20",
+      "placeOfBirth": "Delhi",
+      "height": "5 ft 4 in / 163 cms",
+      "occupation": "Professional",
+      "courses": [
+        {
+          "level": "Professional",
+          "course": "CA — 4 yrs",
+          "stream": "Audit &amp; taxation",
+          "institution": "ICAI",
+          "year": "2019",
+          "pct": "AIR 214"
+        }
+      ]
+    },
+    "chips": {
+      "aadhaarFiles": ["aadhaar-front.jpg", "aadhaar-back.jpg"]
+    },
+    "changeLog": [
+      {
+        "id": "demo-mobile-1",
+        "fieldKey": "mobile",
+        "label": "Mobile",
+        "from": "98••• ••771",
+        "to": "98••• ••164",
+        "at": "07 Sep 2026, 11:24 am",
+        "by": "Neha Sharma",
+        "via": "OTP verified"
+      }
+    ]
+  }
+}
+Note: values may include any key from intakeFormData SECTION_BLOCKS (personal→casesheet). Do not invent alternate names. Empty P0 intake returns values: {} and chips: {}.</t>
+  </si>
+  <si>
+    <t>IntakeFormTab values/chips/changeLog + Fill form progress</t>
+  </si>
+  <si>
+    <t>Get Intake Section</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/intake/sections/{sectionKey}</t>
+  </si>
+  <si>
+    <t>Optional slice for one booklet section. sectionKey = SECTIONS_META.key (personal|education|residency|family|siblings|match|essential|medical|declaration|communication|casesheet).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path:
+id
+sectionKey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "sectionKey": "personal",
+    "filled": 28,
+    "total": 40,
+    "percent": 70,
+    "values": {
+      "firstName": "Priya",
+      "lastName": "Raheja",
+      "mobile": "98••• ••164",
+      "email": "priya.raheja@gmail.com"
+    },
+    "chips": {
+      "aadhaarFiles": ["aadhaar-front.jpg", "aadhaar-back.jpg"]
+    }
+  }
+}</t>
+  </si>
+  <si>
+    <t>Active booklet section / SectionEditModal load</t>
+  </si>
+  <si>
+    <t>Get Intake Change Log</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/intake/change-log</t>
+  </si>
+  <si>
+    <t>OTP-verified field history shown on Client record Change summary. Keys match DEMO_CHANGE_LOG / handleOtpVerified log entries.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "items": [
+      {
+        "id": "demo-email-1",
+        "fieldKey": "email",
+        "label": "E-mail",
+        "from": "priya.r@outlook.com",
+        "to": "priya.raheja@gmail.com",
+        "at": "05 Sep 2026, 04:12 pm",
+        "by": "Neha Sharma",
+        "via": "OTP verified"
+      }
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>ClientRecordView changeLog</t>
+  </si>
+  <si>
+    <t>▶ PUT / PATCH Requests — Intake / Profile Create (P2)</t>
+  </si>
+  <si>
+    <t>Save Intake Section Draft (Fill form)</t>
+  </si>
+  <si>
+    <t>Persists section field values while filling (draft). Body values keys must match intakeFormData field keys for that section. chips optional (upload filenames / ids). Personal final commit from Client record still goes through OTP verify API.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path:
+id
+sectionKey — personal|education|residency|family|siblings|match|essential|medical|declaration|communication|casesheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "values": {
+    "firstName": "Priya",
+    "lastName": "Raheja",
+    "mobile": "9876543210",
+    "email": "priya.raheja@gmail.com",
+    "gender": "Female",
+    "maritalStatus": "Never married",
+    "lookingFor": "Groom",
+    "dob": "14 Jul 1995",
+    "placeOfBirth": "Delhi",
+    "religion": "Hindu",
+    "sectCaste": "Agarwal",
+    "height": "5 ft 4 in / 163 cms"
+  },
+  "chips": {
+    "aadhaarFiles": ["aadhaar-front.jpg", "aadhaar-back.jpg"]
+  }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "sectionKey": "personal",
+    "filled": 28,
+    "total": 40,
+    "percent": 70,
+    "overallFilledFields": 145,
+    "overallTotalFields": 270,
+    "overallPercent": 54,
+    "updatedAt": "2025-09-10T12:00:00Z"
+  }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": false,
+  "message": "Validation failed",
+  "errors": [
+    { "field": "firstName", "message": "First name is required" }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>IntakeFillFormView setField / section navigation persistence</t>
+  </si>
+  <si>
+    <t>▶ POST Requests — Intake / Profile Create (P2)</t>
+  </si>
+  <si>
+    <t>Send Intake OTP</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/intake/otp/send</t>
+  </si>
+  <si>
+    <t>PersonalChangeOtpModal Step 1. mode=unlock (edit personal) or mode=commit (save personal / section after changes). FE shows Send OTP → client mobile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "mode": "commit",
+  "sectionKey": "personal",
+  "sectionLabel": "Personal details"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "sent": true,
+    "expiresInSeconds": 300,
+    "maskedMobile": "98••• ••164"
+  }
+}</t>
+  </si>
+  <si>
+    <t>PersonalChangeOtpModal handleSend</t>
+  </si>
+  <si>
+    <t>Verify Intake OTP &amp; Commit Changes</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/intake/otp/verify</t>
+  </si>
+  <si>
+    <t>PersonalChangeOtpModal Step 2 + handleOtpVerified. unlock: sets personalUnlocked. commit: applies values/chips, appends changeLog entries (fieldKey, label, from, to, at, by, via).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "mode": "commit",
+  "otp": "123456",
+  "sectionKey": "personal",
+  "sectionLabel": "Personal details",
+  "changes": [
+    {
+      "key": "mobile",
+      "label": "Mobile",
+      "from": "98••• ••771",
+      "to": "9876543210"
+    }
+  ],
+  "values": {
+    "mobile": "9876543210",
+    "email": "priya.raheja@gmail.com"
+  },
+  "chips": {
+    "aadhaarFiles": ["aadhaar-front.jpg", "aadhaar-back.jpg"]
+  }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "personalUnlocked": false,
+    "applied": true,
+    "changeLogEntries": [
+      {
+        "id": "cl-1",
+        "fieldKey": "mobile",
+        "label": "Mobile",
+        "from": "98••• ••771",
+        "to": "9876543210",
+        "at": "10 Sep 2026, 06:12 pm",
+        "by": "Neha Sharma",
+        "via": "OTP verified"
+      }
+    ],
+    "overallFilledFields": 146,
+    "overallTotalFields": 270,
+    "overallPercent": 54
+  }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": false,
+  "message": "Enter the OTP sent to the client.",
+  "errors": [
+    { "field": "otp", "message": "Enter the OTP sent to the client." }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>PersonalChangeOtpModal Verify &amp; update / SectionEditModal Save &amp; send OTP flow</t>
+  </si>
+  <si>
+    <t>Upload Intake Document Chip</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/intake/uploads</t>
+  </si>
+  <si>
+    <t>Upload for fields with type=upload (e.g. panNo, aadhaarNo). Returns filename/id pushed into chips[chipsKey] (FE: aadhaarFiles).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multipart/form-data:
+fieldKey: aadhaarNo
+chipsKey: aadhaarFiles
+file: (binary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "fieldKey": "aadhaarNo",
+    "chipsKey": "aadhaarFiles",
+    "fileName": "aadhaar-front.jpg",
+    "fileId": "file-123"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Intake upload fields / removeChip list</t>
+  </si>
+  <si>
+    <t>Intake note: Full field catalog lives in frontend intakeFormData.js (SECTION_BLOCKS). API stores/returns the same camelCase keys — do not rename (firstName stays firstName, not client_name). Section tips, booklet labels, Fill/Record toggle are FE-static. Advance P2→P3 = PATCH /pipeline/leads/{id}/stage with fromStage P2, toStage P3 (already on PAGE 1).</t>
+  </si>
+  <si>
     <t>UPCOMING (append in this same sheet — no separate tabs)</t>
   </si>
   <si>
-    <t>Next tabs one-by-one: Profile Create / Intake (P2) → Visits (P3) → Package (P4) → Discounts → Documents → Notes &amp; RM Flags → Audit → Payments (P5) → P6 Checklist. Same rules: FE static UI; BE dynamic fields matching frontend keys; premium (not starred) for Star.</t>
-  </si>
-  <si>
-    <t>Document version: 1.4  |  Pages: Pipeline Board + Add P0 + Deal Overview  |  Field fix: starred → premium  |  Status: Ready for review</t>
+    <t>Next tabs one-by-one: Visits / Video Call (P3) → Package &amp; Quote (P4) → Discounts → Documents &amp; KYC → Notes &amp; RM Flags → Audit → Payments (P5) → P6 Checklist. Same rules: FE static UI; BE dynamic fields matching frontend keys.</t>
+  </si>
+  <si>
+    <t>Document version: 1.5  |  Pages: Board + Add P0 + Overview + Intake (P2)  |  Status: Ready for review</t>
   </si>
 </sst>
 </file>
@@ -1654,7 +2011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3089,53 +3446,493 @@
         <v>174</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="25" t="s">
+    <row r="68" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B68" s="25"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="25"/>
-      <c r="E68" s="25"/>
-      <c r="F68" s="25"/>
-      <c r="G68" s="25"/>
-      <c r="H68" s="25"/>
-      <c r="I68" s="25"/>
-      <c r="J68" s="25"/>
-      <c r="K68" s="25"/>
-    </row>
-    <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="26" t="s">
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+    </row>
+    <row r="69" ht="48" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26"/>
-      <c r="H69" s="26"/>
-      <c r="I69" s="26"/>
-      <c r="J69" s="26"/>
-      <c r="K69" s="26"/>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="27" t="s">
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+    </row>
+    <row r="71" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B70" s="27"/>
-      <c r="C70" s="27"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="27"/>
-      <c r="J70" s="27"/>
-      <c r="K70" s="27"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="7"/>
+      <c r="H71" s="7"/>
+      <c r="I71" s="7"/>
+      <c r="J71" s="7"/>
+      <c r="K71" s="7"/>
+    </row>
+    <row r="72" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J72" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K72" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="9">
+        <v>1</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I73" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="J73" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K73" s="10" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="74" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="12">
+        <v>2</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F74" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="H74" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I74" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="J74" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K74" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="75" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="9">
+        <v>3</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="J75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K75" s="10" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="77" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="B77" s="19"/>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="19"/>
+      <c r="K77" s="19"/>
+    </row>
+    <row r="78" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J78" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K78" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="9">
+        <v>1</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C79" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="I79" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="J79" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="K79" s="10" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="81" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="B81" s="15"/>
+      <c r="C81" s="15"/>
+      <c r="D81" s="15"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="15"/>
+      <c r="G81" s="15"/>
+      <c r="H81" s="15"/>
+      <c r="I81" s="15"/>
+      <c r="J81" s="15"/>
+      <c r="K81" s="15"/>
+    </row>
+    <row r="82" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J82" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K82" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" ht="88" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="9">
+        <v>1</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C83" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="I83" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="J83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K83" s="10" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="84" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="12">
+        <v>2</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="C84" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D84" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="F84" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G84" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H84" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="I84" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="J84" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="K84" s="13" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="85" ht="99" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="9">
+        <v>3</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C85" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I85" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="J85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K85" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="86" ht="44" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="B86" s="18"/>
+      <c r="C86" s="18"/>
+      <c r="D86" s="18"/>
+      <c r="E86" s="18"/>
+      <c r="F86" s="18"/>
+      <c r="G86" s="18"/>
+      <c r="H86" s="18"/>
+      <c r="I86" s="18"/>
+      <c r="J86" s="18"/>
+      <c r="K86" s="18"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="B89" s="25"/>
+      <c r="C89" s="25"/>
+      <c r="D89" s="25"/>
+      <c r="E89" s="25"/>
+      <c r="F89" s="25"/>
+      <c r="G89" s="25"/>
+      <c r="H89" s="25"/>
+      <c r="I89" s="25"/>
+      <c r="J89" s="25"/>
+      <c r="K89" s="25"/>
+    </row>
+    <row r="90" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="B90" s="26"/>
+      <c r="C90" s="26"/>
+      <c r="D90" s="26"/>
+      <c r="E90" s="26"/>
+      <c r="F90" s="26"/>
+      <c r="G90" s="26"/>
+      <c r="H90" s="26"/>
+      <c r="I90" s="26"/>
+      <c r="J90" s="26"/>
+      <c r="K90" s="26"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="B91" s="27"/>
+      <c r="C91" s="27"/>
+      <c r="D91" s="27"/>
+      <c r="E91" s="27"/>
+      <c r="F91" s="27"/>
+      <c r="G91" s="27"/>
+      <c r="H91" s="27"/>
+      <c r="I91" s="27"/>
+      <c r="J91" s="27"/>
+      <c r="K91" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="29">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
@@ -3158,7 +3955,13 @@
     <mergeCell ref="A63:K63"/>
     <mergeCell ref="A68:K68"/>
     <mergeCell ref="A69:K69"/>
-    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="A71:K71"/>
+    <mergeCell ref="A77:K77"/>
+    <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A86:K86"/>
+    <mergeCell ref="A89:K89"/>
+    <mergeCell ref="A90:K90"/>
+    <mergeCell ref="A91:K91"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/MML_Sales_API_Documentation.xlsx
+++ b/docs/MML_Sales_API_Documentation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="279">
   <si>
     <t>MML Sales CRM — API Documentation (Client Share)</t>
   </si>
@@ -1402,13 +1402,406 @@
     <t>Intake note: Full field catalog lives in frontend intakeFormData.js (SECTION_BLOCKS). API stores/returns the same camelCase keys — do not rename (firstName stays firstName, not client_name). Section tips, booklet labels, Fill/Record toggle are FE-static. Advance P2→P3 = PATCH /pipeline/leads/{id}/stage with fromStage P2, toStage P3 (already on PAGE 1).</t>
   </si>
   <si>
+    <t>PAGE 5: Deal Detail — Visits &amp; Meetings (P3) — File: deal-tabs/VisitsMeetingsTab.jsx</t>
+  </si>
+  <si>
+    <t>Default tab when stageId=P3. Same design as desk/HomeOfficeVisitsPage.jsx. Dynamic: visit details form (visitType, date, slot, client, attend, vehicle), mandatory capture checklist, visits list + lastAction (summary/notes/recording/transcript). Filters period + typeFilter. FE-only: section titles, ProgressMeter colors, StatusPill tones can be mapped from status. Move P3→P4 = existing PATCH .../stage.</t>
+  </si>
+  <si>
+    <t>▶ GET Requests — Visits &amp; Meetings (P3)</t>
+  </si>
+  <si>
+    <t>Get Visits Tab (deal)</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/visits</t>
+  </si>
+  <si>
+    <t>Loads VisitsMeetingsTab: active/scheduled visit details, capture checklist, and upcoming/recent visits list. Field names match FE state + VISITS / CAPTURE_ITEMS objects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path: id
+Query (list filters — FE: period, typeFilter):
+period — month|quarter
+type — all|Home visit|Office visit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "p3-1",
+    "stageId": "P3",
+    "dealCode": "MML-D-10434",
+    "locationNote": "Greater Kailash · GPS required",
+    "activeVisit": {
+      "id": "visit-1",
+      "visitType": "Home visit",
+      "date": "2026-07-02",
+      "slot": "11:00 AM – 1:00 PM",
+      "client": "Aditya Verma",
+      "attend": "Client + both parents",
+      "vehicle": "Yes — branch car",
+      "status": "Scheduled",
+      "progressPercent": 35
+    },
+    "capture": [
+      {
+        "title": "House / GPS photo",
+        "note": "Taken at the door with location accuracy under 15m.",
+        "status": "Captured",
+        "done": true
+      },
+      {
+        "title": "Selfie with client",
+        "note": "Staff and client in frame. Used for in-person verification.",
+        "status": "Captured",
+        "done": true
+      },
+      {
+        "title": "Staff activity form",
+        "note": "Who attended, talking points and next action.",
+        "status": "Pending",
+        "done": false,
+        "pending": true
+      },
+      {
+        "title": "Advance booking call log",
+        "note": "Call confirming the slot is logged against the deal.",
+        "status": "Not started",
+        "done": false
+      }
+    ],
+    "captureDone": 2,
+    "captureTotal": 4,
+    "visits": [
+      {
+        "id": "visit-1",
+        "date": "02 Jul",
+        "client": "Aditya Verma",
+        "type": "Home visit",
+        "executive": "Rohit Khanna",
+        "capture": "2 of 4",
+        "vehicle": "Yes",
+        "status": "Scheduled",
+        "lastAction": {
+          "summary": "Family open to Premium; prefers GK / South Delhi matches",
+          "notes": "Discussed package options; parents want evening slots",
+          "recording": "Not recorded yet",
+          "transcript": "Not available"
+        }
+      },
+      {
+        "id": "visit-2",
+        "date": "14 Jul",
+        "client": "Sanjay Mehta",
+        "type": "Office visit",
+        "executive": "Pooja Sharma",
+        "capture": "4 of 4",
+        "vehicle": "No",
+        "status": "Completed",
+        "lastAction": {
+          "summary": "Ready to shortlist 5 profiles this week",
+          "notes": "Agreed on Classic package; KYC pending",
+          "recording": "18 min · Office visit",
+          "transcript": "Full transcript ready (12 pages)"
+        }
+      }
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>VisitsMeetingsTab — details form + capture + DeskTable</t>
+  </si>
+  <si>
+    <t>Get Visit by Id</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/visits/{visitId}</t>
+  </si>
+  <si>
+    <t>Single visit with capture + lastAction detail (hover icons: summary, notes, recording, transcript).</t>
+  </si>
+  <si>
+    <t>Path: id, visitId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "visit-2",
+    "date": "14 Jul",
+    "client": "Sanjay Mehta",
+    "type": "Office visit",
+    "executive": "Pooja Sharma",
+    "capture": "4 of 4",
+    "vehicle": "No",
+    "status": "Completed",
+    "visitType": "Office visit",
+    "slot": "2:00 PM – 4:00 PM",
+    "attend": "Client only",
+    "lastAction": {
+      "summary": "Ready to shortlist 5 profiles this week",
+      "notes": "Agreed on Classic package; KYC pending",
+      "recording": "18 min · Office visit",
+      "transcript": "Full transcript ready (12 pages)"
+    },
+    "captureItems": [
+      {
+        "title": "House / GPS photo",
+        "status": "Captured",
+        "done": true
+      }
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>LastActionIcons hover / visit row open</t>
+  </si>
+  <si>
+    <t>▶ POST Requests — Visits &amp; Meetings (P3)</t>
+  </si>
+  <si>
+    <t>Schedule / Create Visit</t>
+  </si>
+  <si>
+    <t>Creates a visit from Visit details form fields (same keys as FE useState: visitType, date, slot, client, attend, vehicle).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "visitType": "Home visit",
+  "date": "2026-07-02",
+  "slot": "11:00 AM – 1:00 PM",
+  "client": "Aditya Verma",
+  "attend": "Client + both parents",
+  "vehicle": "Yes — branch car"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "visit-3",
+    "visitType": "Home visit",
+    "date": "2026-07-02",
+    "slot": "11:00 AM – 1:00 PM",
+    "client": "Aditya Verma",
+    "attend": "Client + both parents",
+    "vehicle": "Yes — branch car",
+    "status": "Scheduled",
+    "executive": "Rohit Khanna",
+    "capture": "0 of 4",
+    "lastAction": {
+      "summary": "Visit not started",
+      "notes": "No notes yet",
+      "recording": "Not recorded yet",
+      "transcript": "Not available"
+    }
+  }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": false,
+  "message": "Validation failed",
+  "errors": [
+    { "field": "date", "message": "Date is required" },
+    { "field": "slot", "message": "Time slot is required" }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Visit details form save / schedule</t>
+  </si>
+  <si>
+    <t>Start Visit</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/visits/{visitId}/start</t>
+  </si>
+  <si>
+    <t>PrimaryButton Start Visit — marks visit in progress and unlocks capture checklist (FE toast: Visit started. Capture checklist is live.).</t>
+  </si>
+  <si>
+    <t>— (no body) or {}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "visit-1",
+    "status": "In progress",
+    "captureLive": true
+  }
+}</t>
+  </si>
+  <si>
+    <t>PrimaryButton Start Visit</t>
+  </si>
+  <si>
+    <t>Reschedule Visit</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/visits/{visitId}/reschedule</t>
+  </si>
+  <si>
+    <t>OutlineButton Reschedule — updates date and/or slot (FE: Reschedule slot opened).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "date": "2026-07-05",
+  "slot": "2:00 PM – 4:00 PM"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "visit-1",
+    "date": "2026-07-05",
+    "slot": "2:00 PM – 4:00 PM",
+    "status": "Scheduled"
+  }
+}</t>
+  </si>
+  <si>
+    <t>OutlineButton Reschedule</t>
+  </si>
+  <si>
+    <t>▶ PUT / PATCH Requests — Visits &amp; Meetings (P3)</t>
+  </si>
+  <si>
+    <t>Update Visit Details</t>
+  </si>
+  <si>
+    <t>Updates active visit form fields (visitType, date, slot, client, attend, vehicle).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "visitType": "Office visit",
+  "date": "2026-07-02",
+  "slot": "5:00 PM – 7:00 PM",
+  "client": "Aditya Verma",
+  "attend": "Client + both parents",
+  "vehicle": "No — staff travel"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "visit-1",
+    "visitType": "Office visit",
+    "date": "2026-07-02",
+    "slot": "5:00 PM – 7:00 PM",
+    "client": "Aditya Verma",
+    "attend": "Client + both parents",
+    "vehicle": "No — staff travel",
+    "status": "Scheduled"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Visit details Field inputs</t>
+  </si>
+  <si>
+    <t>Toggle Capture Checklist Item</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/visits/{visitId}/capture</t>
+  </si>
+  <si>
+    <t>CheckRow toggleCapture(title). Matches CAPTURE_ITEMS: title + done; BE sets status Captured|Pending (FE also maps tone).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "title": "Staff activity form",
+  "done": true
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "visit-1",
+    "capture": [
+      {
+        "title": "House / GPS photo",
+        "status": "Captured",
+        "done": true
+      },
+      {
+        "title": "Selfie with client",
+        "status": "Captured",
+        "done": true
+      },
+      {
+        "title": "Staff activity form",
+        "status": "Captured",
+        "done": true,
+        "pending": false
+      },
+      {
+        "title": "Advance booking call log",
+        "status": "Not started",
+        "done": false
+      }
+    ],
+    "captureDone": 3,
+    "captureTotal": 4,
+    "captureLabel": "3 of 4"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Mandatory capture CheckRow onToggle</t>
+  </si>
+  <si>
+    <t>Update Visit Last Action / Notes</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/visits/{visitId}/last-action</t>
+  </si>
+  <si>
+    <t>Updates lastAction object keys used by LastActionIcons: summary, notes, recording, transcript.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "summary": "Family open to Premium; prefers GK / South Delhi matches",
+  "notes": "Discussed package options; parents want evening slots",
+  "recording": "Not recorded yet",
+  "transcript": "Not available"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "visit-1",
+    "lastAction": {
+      "summary": "Family open to Premium; prefers GK / South Delhi matches",
+      "notes": "Discussed package options; parents want evening slots",
+      "recording": "Not recorded yet",
+      "transcript": "Not available"
+    }
+  }
+}</t>
+  </si>
+  <si>
+    <t>Meeting notes / recording / transcript data behind action icons</t>
+  </si>
+  <si>
+    <t>P3 note: Visit type options = Home visit | Office visit. Slot options = 11:00 AM – 1:00 PM | 2:00 PM – 4:00 PM | 5:00 PM – 7:00 PM (FE select). Capture titles must match CAPTURE_ITEMS exactly. Table columns: date, client, type, executive, capture, vehicle, status, lastAction. Advance P3→P4 = PATCH /pipeline/leads/{id}/stage.</t>
+  </si>
+  <si>
     <t>UPCOMING (append in this same sheet — no separate tabs)</t>
   </si>
   <si>
-    <t>Next tabs one-by-one: Visits / Video Call (P3) → Package &amp; Quote (P4) → Discounts → Documents &amp; KYC → Notes &amp; RM Flags → Audit → Payments (P5) → P6 Checklist. Same rules: FE static UI; BE dynamic fields matching frontend keys.</t>
-  </si>
-  <si>
-    <t>Document version: 1.5  |  Pages: Board + Add P0 + Overview + Intake (P2)  |  Status: Ready for review</t>
+    <t>Next tabs one-by-one: Package &amp; Quote (P4) → Discounts → Documents &amp; KYC → Notes &amp; RM Flags → Audit → Payments (P5) → P6 Checklist. Same rules: FE static UI; BE dynamic fields matching frontend keys.</t>
+  </si>
+  <si>
+    <t>Document version: 1.6  |  Pages: Board + Add P0 + Overview + Intake (P2) + Visits (P3)  |  Status: Ready for review</t>
   </si>
 </sst>
 </file>
@@ -2011,7 +2404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3886,53 +4279,528 @@
       <c r="J86" s="18"/>
       <c r="K86" s="18"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" s="25" t="s">
+    <row r="89" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B89" s="25"/>
-      <c r="C89" s="25"/>
-      <c r="D89" s="25"/>
-      <c r="E89" s="25"/>
-      <c r="F89" s="25"/>
-      <c r="G89" s="25"/>
-      <c r="H89" s="25"/>
-      <c r="I89" s="25"/>
-      <c r="J89" s="25"/>
-      <c r="K89" s="25"/>
-    </row>
-    <row r="90" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90" s="26" t="s">
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="5"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="5"/>
+      <c r="K89" s="5"/>
+    </row>
+    <row r="90" ht="48" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B90" s="26"/>
-      <c r="C90" s="26"/>
-      <c r="D90" s="26"/>
-      <c r="E90" s="26"/>
-      <c r="F90" s="26"/>
-      <c r="G90" s="26"/>
-      <c r="H90" s="26"/>
-      <c r="I90" s="26"/>
-      <c r="J90" s="26"/>
-      <c r="K90" s="26"/>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" s="27" t="s">
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6"/>
+    </row>
+    <row r="92" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="B91" s="27"/>
-      <c r="C91" s="27"/>
-      <c r="D91" s="27"/>
-      <c r="E91" s="27"/>
-      <c r="F91" s="27"/>
-      <c r="G91" s="27"/>
-      <c r="H91" s="27"/>
-      <c r="I91" s="27"/>
-      <c r="J91" s="27"/>
-      <c r="K91" s="27"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="7"/>
+      <c r="G92" s="7"/>
+      <c r="H92" s="7"/>
+      <c r="I92" s="7"/>
+      <c r="J92" s="7"/>
+      <c r="K92" s="7"/>
+    </row>
+    <row r="93" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J93" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K93" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" s="9">
+        <v>1</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="H94" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I94" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="J94" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K94" s="10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="95" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="12">
+        <v>2</v>
+      </c>
+      <c r="B95" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="C95" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D95" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="F95" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G95" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="H95" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I95" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="J95" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K95" s="13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="97" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="B97" s="15"/>
+      <c r="C97" s="15"/>
+      <c r="D97" s="15"/>
+      <c r="E97" s="15"/>
+      <c r="F97" s="15"/>
+      <c r="G97" s="15"/>
+      <c r="H97" s="15"/>
+      <c r="I97" s="15"/>
+      <c r="J97" s="15"/>
+      <c r="K97" s="15"/>
+    </row>
+    <row r="98" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J98" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K98" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="9">
+        <v>1</v>
+      </c>
+      <c r="B99" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I99" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="J99" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="K99" s="10" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="100" ht="88" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" s="12">
+        <v>2</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="C100" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="E100" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="F100" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G100" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="H100" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="I100" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="J100" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K100" s="13" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="101" ht="99" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="9">
+        <v>3</v>
+      </c>
+      <c r="B101" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="C101" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="I101" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="J101" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K101" s="10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="103" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="B103" s="19"/>
+      <c r="C103" s="19"/>
+      <c r="D103" s="19"/>
+      <c r="E103" s="19"/>
+      <c r="F103" s="19"/>
+      <c r="G103" s="19"/>
+      <c r="H103" s="19"/>
+      <c r="I103" s="19"/>
+      <c r="J103" s="19"/>
+      <c r="K103" s="19"/>
+    </row>
+    <row r="104" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H104" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I104" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J104" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K104" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105" ht="143" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" s="9">
+        <v>1</v>
+      </c>
+      <c r="B105" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C105" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D105" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="F105" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G105" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="I105" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="J105" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K105" s="10" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="106" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" s="12">
+        <v>2</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="C106" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D106" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="E106" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="F106" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G106" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="H106" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="I106" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="J106" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K106" s="13" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="107" ht="132" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" s="9">
+        <v>3</v>
+      </c>
+      <c r="B107" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C107" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="I107" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="J107" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K107" s="10" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="108" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="B108" s="18"/>
+      <c r="C108" s="18"/>
+      <c r="D108" s="18"/>
+      <c r="E108" s="18"/>
+      <c r="F108" s="18"/>
+      <c r="G108" s="18"/>
+      <c r="H108" s="18"/>
+      <c r="I108" s="18"/>
+      <c r="J108" s="18"/>
+      <c r="K108" s="18"/>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="B111" s="25"/>
+      <c r="C111" s="25"/>
+      <c r="D111" s="25"/>
+      <c r="E111" s="25"/>
+      <c r="F111" s="25"/>
+      <c r="G111" s="25"/>
+      <c r="H111" s="25"/>
+      <c r="I111" s="25"/>
+      <c r="J111" s="25"/>
+      <c r="K111" s="25"/>
+    </row>
+    <row r="112" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B112" s="26"/>
+      <c r="C112" s="26"/>
+      <c r="D112" s="26"/>
+      <c r="E112" s="26"/>
+      <c r="F112" s="26"/>
+      <c r="G112" s="26"/>
+      <c r="H112" s="26"/>
+      <c r="I112" s="26"/>
+      <c r="J112" s="26"/>
+      <c r="K112" s="26"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="B113" s="27"/>
+      <c r="C113" s="27"/>
+      <c r="D113" s="27"/>
+      <c r="E113" s="27"/>
+      <c r="F113" s="27"/>
+      <c r="G113" s="27"/>
+      <c r="H113" s="27"/>
+      <c r="I113" s="27"/>
+      <c r="J113" s="27"/>
+      <c r="K113" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="35">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
@@ -3961,7 +4829,13 @@
     <mergeCell ref="A86:K86"/>
     <mergeCell ref="A89:K89"/>
     <mergeCell ref="A90:K90"/>
-    <mergeCell ref="A91:K91"/>
+    <mergeCell ref="A92:K92"/>
+    <mergeCell ref="A97:K97"/>
+    <mergeCell ref="A103:K103"/>
+    <mergeCell ref="A108:K108"/>
+    <mergeCell ref="A111:K111"/>
+    <mergeCell ref="A112:K112"/>
+    <mergeCell ref="A113:K113"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/MML_Sales_API_Documentation.xlsx
+++ b/docs/MML_Sales_API_Documentation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1061" uniqueCount="486">
   <si>
     <t>MML Sales CRM — API Documentation (Client Share)</t>
   </si>
@@ -1795,13 +1795,1217 @@
     <t>P3 note: Visit type options = Home visit | Office visit. Slot options = 11:00 AM – 1:00 PM | 2:00 PM – 4:00 PM | 5:00 PM – 7:00 PM (FE select). Capture titles must match CAPTURE_ITEMS exactly. Table columns: date, client, type, executive, capture, vehicle, status, lastAction. Advance P3→P4 = PATCH /pipeline/leads/{id}/stage.</t>
   </si>
   <si>
-    <t>UPCOMING (append in this same sheet — no separate tabs)</t>
-  </si>
-  <si>
-    <t>Next tabs one-by-one: Package &amp; Quote (P4) → Discounts → Documents &amp; KYC → Notes &amp; RM Flags → Audit → Payments (P5) → P6 Checklist. Same rules: FE static UI; BE dynamic fields matching frontend keys.</t>
-  </si>
-  <si>
-    <t>Document version: 1.6  |  Pages: Board + Add P0 + Overview + Intake (P2) + Visits (P3)  |  Status: Ready for review</t>
+    <t>PAGE 6: Deal Detail — Package &amp; Quote (P4) — File: deal-tabs/PackageQuoteTab.jsx</t>
+  </si>
+  <si>
+    <t>Default tab when stageId=P4. Sections: package catalogue (PACKAGES), Discount Approvals (embedded), Upsell banner (mostly FE/AI later), Quotation, Progressive data reveal, Cross-branch price check. Selected package key comes from DealDetailPage selectedPackage.key (basic|premium|exclusive). Move P4→P5 requires package selected (FE gate) then PATCH .../stage.</t>
+  </si>
+  <si>
+    <t>▶ GET Requests — Package &amp; Quote (P4)</t>
+  </si>
+  <si>
+    <t>Get Package &amp; Quote Tab</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/package</t>
+  </si>
+  <si>
+    <t>Full P4 tab payload. packages[] keys match PACKAGES (key, name, price, subtitle, features[], upsellBadge). selectedKey = selected package. quote + discountApprovals + dataReveal + crossBranchPriceCheck from QuotationCard / DiscountApprovalsCard / DataRevealCard.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "p4-1",
+    "stageId": "P4",
+    "dealCode": "MML-D-10428",
+    "currency": "INR",
+    "selectedKey": "premium",
+    "packages": [
+      {
+        "key": "basic",
+        "name": "Basic",
+        "price": "₹25,000",
+        "subtitle": "6 months · junior RM",
+        "features": [
+          { "label": "Profile creation &amp; curation", "included": true },
+          { "label": "Verified Report", "included": false }
+        ]
+      },
+      {
+        "key": "premium",
+        "name": "Premium",
+        "price": "₹51,000",
+        "subtitle": "12 months, senior RM only",
+        "features": [
+          { "label": "Everything in Classic", "included": true },
+          { "label": "Dedicated senior RM", "included": false }
+        ]
+      },
+      {
+        "key": "exclusive",
+        "name": "Exclusive",
+        "price": "₹1,25,000",
+        "subtitle": "12 months, senior RM only",
+        "upsellBadge": "+74,000",
+        "features": [
+          { "label": "Everything in Premium", "included": true },
+          { "label": "Founder-approved special access", "included": true }
+        ]
+      }
+    ],
+    "discountApprovals": [
+      {
+        "id": "da-1",
+        "raised": "28 July",
+        "requested": "₹51,000",
+        "discount": "14.7%",
+        "approver": "Pooja Sharma",
+        "level": "Branch Head",
+        "status": "Pending"
+      },
+      {
+        "id": "da-2",
+        "raised": "v2",
+        "requested": "₹48,000",
+        "discount": "5.9%",
+        "approver": "Vinay Gupta",
+        "level": "Team Lead",
+        "status": "Approved"
+      }
+    ],
+    "quote": {
+      "versionLabel": "Draft v2",
+      "items": [
+        {
+          "item": "Premium Package",
+          "note": "12 months membership",
+          "type": "Base",
+          "qty": 1,
+          "quoted": "₹51,000",
+          "rate": "₹51,000"
+        },
+        {
+          "item": "Kundli / horoscope service",
+          "note": "Redeemable against wallet credits",
+          "type": "Base",
+          "qty": 1,
+          "quoted": "₹51,000",
+          "rate": "₹2,500"
+        },
+        {
+          "item": "Verified Profile Report",
+          "note": "Included in Premium – no charge",
+          "type": "Base",
+          "qty": 1,
+          "quoted": "₹51,000",
+          "rate": "₹0"
+        }
+      ],
+      "summary": [
+        { "label": "Subtotal", "value": "₹53,500" },
+        { "label": "Approved discount", "value": "-₹7,500" },
+        { "label": "Wallet credits applied (referral)", "value": "-₹1000" },
+        { "label": "GST @ 18%", "value": "₹8,100" }
+      ],
+      "totalPayable": "₹53,100"
+    },
+    "dataReveal": [
+      {
+        "label": "Level 1 — Photo",
+        "note": "All packages · on shortlist",
+        "done": true
+      },
+      {
+        "label": "Level 2 — Basic details",
+        "note": "All packages · age, height, education",
+        "done": true
+      },
+      {
+        "label": "Level 3 — Contact",
+        "note": "Premium &amp; Exclusive · RM approval required",
+        "done": true
+      },
+      {
+        "label": "Level 4 — Address",
+        "note": "Exclusive only · Branch Head approval",
+        "done": false
+      }
+    ],
+    "crossBranchPriceCheck": {
+      "title": "Client contacted Rajouri branch.",
+      "detail": "Quoted ₹51,000 there too. Flagged to your Branch Head on 29 Jun"
+    }
+  }
+}</t>
+  </si>
+  <si>
+    <t>PackageQuoteTab full layout</t>
+  </si>
+  <si>
+    <t>Get Discount Approvals</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/discounts</t>
+  </si>
+  <si>
+    <t>Discount approval rows only (same shape as PackageQuoteTab DiscountApprovalsCard / DiscountApprovalsTab INITIAL_APPROVALS).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "items": [
+      {
+        "id": "da-1",
+        "raised": "28 July",
+        "requested": "₹51,000",
+        "discount": "14.7%",
+        "approver": "Pooja Sharma",
+        "level": "Branch Head",
+        "status": "Pending"
+      }
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Discount Approvals table</t>
+  </si>
+  <si>
+    <t>Preview Quote PDF</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/quote/preview</t>
+  </si>
+  <si>
+    <t>Preview PDF button — returns file or download URL (FE toast: Generating quote PDF preview...).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binary PDF
+OR
+{
+  "success": true,
+  "data": {
+    "downloadUrl": "https://...",
+    "expiresAt": "2026-07-02T12:00:00Z"
+  }
+}</t>
+  </si>
+  <si>
+    <t>QuotationCard Preview PDF</t>
+  </si>
+  <si>
+    <t>▶ POST Requests — Package &amp; Quote (P4)</t>
+  </si>
+  <si>
+    <t>Select Package</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/package/select</t>
+  </si>
+  <si>
+    <t>PackageCard Select → onPackageSelect(pkg). Body key matches PACKAGES.key (basic|premium|exclusive). Required before Move to P5 in DealDetailPage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "key": "premium"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "selectedKey": "premium",
+    "name": "Premium",
+    "price": "₹51,000"
+  }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": false,
+  "message": "Invalid package key"
+}</t>
+  </si>
+  <si>
+    <t>PackageCard Select / DealDetailPage selectedPackage</t>
+  </si>
+  <si>
+    <t>Request Discount</t>
+  </si>
+  <si>
+    <t>Request discount modal fields: requested, discount, level (Team Lead|Branch Head|Founder). Creates row status Pending; approver assigned by level matrix.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "requested": "51000",
+  "discount": "10",
+  "level": "Team Lead"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "da-3",
+    "raised": "Just now",
+    "requested": "₹51,000",
+    "discount": "10%",
+    "approver": "Vinay Gupta",
+    "level": "Team Lead",
+    "status": "Pending"
+  }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": false,
+  "message": "Please add requested amount and discount.",
+  "errors": [
+    { "field": "requested", "message": "Please add requested amount and discount." }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>DiscountApprovalsCard Request discount form</t>
+  </si>
+  <si>
+    <t>Add Quote Add-on</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/quote/items</t>
+  </si>
+  <si>
+    <t>Add add-on modal: itemName → item, quoted → quoted/rate, type Add-on, qty 1 (QuotationCard handleSave).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "item": "Photo reshoot",
+  "quoted": "2500"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "item": "Photo reshoot",
+    "note": "Added to this quote",
+    "type": "Add-on",
+    "qty": 1,
+    "quoted": "₹2,500",
+    "rate": "₹2,500",
+    "totalPayable": "₹55,600"
+  }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": false,
+  "message": "Please add an item and amount."
+}</t>
+  </si>
+  <si>
+    <t>QuotationCard Add add-on</t>
+  </si>
+  <si>
+    <t>Send Quote to Client</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/quote/send</t>
+  </si>
+  <si>
+    <t>Send quote to client button (FE toast: Quote sent to client.). Typically allowed after discount approved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "channel": "email"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "sent": true,
+    "sentAt": "2026-07-02T11:00:00Z"
+  }
+}</t>
+  </si>
+  <si>
+    <t>QuotationCard Send quote to client</t>
+  </si>
+  <si>
+    <t>Create Payment Link</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/quote/payment-link</t>
+  </si>
+  <si>
+    <t>Payment link button — returns shareable URL (FE: Payment link copied and ready to share).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "paymentUrl": "https://pay.example/mml/...",
+    "amount": "₹53,100"
+  }
+}</t>
+  </si>
+  <si>
+    <t>QuotationCard Payment link</t>
+  </si>
+  <si>
+    <t>▶ PUT / PATCH Requests — Package &amp; Quote (P4)</t>
+  </si>
+  <si>
+    <t>Toggle Data Reveal Level</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/package/data-reveal</t>
+  </si>
+  <si>
+    <t>DataRevealCard toggleLevel(label). Keys: label + done (DATA_REVEAL_LEVELS).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "label": "Level 4 — Address",
+  "done": true
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "dataReveal": [
+      {
+        "label": "Level 1 — Photo",
+        "note": "All packages · on shortlist",
+        "done": true
+      },
+      {
+        "label": "Level 2 — Basic details",
+        "note": "All packages · age, height, education",
+        "done": true
+      },
+      {
+        "label": "Level 3 — Contact",
+        "note": "Premium &amp; Exclusive · RM approval required",
+        "done": true
+      },
+      {
+        "label": "Level 4 — Address",
+        "note": "Exclusive only · Branch Head approval",
+        "done": true
+      }
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>Progressive data reveal checklist</t>
+  </si>
+  <si>
+    <t>Update Discount Approval Status</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/discounts/{discountId}</t>
+  </si>
+  <si>
+    <t>Approver action — status Pending|Approved (and reject if product adds it). Updates quote Approved discount line when approved.</t>
+  </si>
+  <si>
+    <t>Path: id, discountId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "status": "Approved"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "da-1",
+    "status": "Approved",
+    "approver": "Pooja Sharma",
+    "level": "Branch Head"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Discount approval workflow (authority matrix)</t>
+  </si>
+  <si>
+    <t>P4 note: Package keys = basic|premium|exclusive. Discount levels = Team Lead|Branch Head|Founder. Quote line keys = item, note, type, qty, quoted, rate. AI pitch buttons are FE toast/coming soon — optional later. Currency INR / NRI USD toggle: INR live; USD coming soon on FE. Advance P4→P5 = select package then PATCH .../stage.</t>
+  </si>
+  <si>
+    <t>PAGE 7: Deal Detail — Documents &amp; KYC — File: deal-tabs/DocumentsKycTab.jsx</t>
+  </si>
+  <si>
+    <t>Also embedded in Intake Documents &amp; KYC modal (getSelectedDocs = docs where done=true). Doc row keys: id, label, fileName, done, mandatory.</t>
+  </si>
+  <si>
+    <t>▶ GET Requests — Documents &amp; KYC</t>
+  </si>
+  <si>
+    <t>Get Documents &amp; KYC List</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/documents</t>
+  </si>
+  <si>
+    <t>Document checklist rows matching INITIAL_DOCUMENTS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "items": [
+      {
+        "id": "doc-1",
+        "label": "Aadhaar card — client",
+        "fileName": "",
+        "done": false,
+        "mandatory": true
+      },
+      {
+        "id": "doc-2",
+        "label": "PAN card — client",
+        "fileName": "pan-front.jpg",
+        "done": true,
+        "mandatory": true
+      }
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>DocumentsKycTab list / Intake selected docs</t>
+  </si>
+  <si>
+    <t>▶ POST Requests — Documents &amp; KYC</t>
+  </si>
+  <si>
+    <t>Add Document Row</t>
+  </si>
+  <si>
+    <t>Add Row modal: nameDraft → label, mandatoryDraft → mandatory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "label": "Passport — client",
+  "mandatory": false
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "doc-8",
+    "label": "Passport — client",
+    "fileName": "",
+    "done": false,
+    "mandatory": false
+  }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": false,
+  "message": "Please enter a document name."
+}</t>
+  </si>
+  <si>
+    <t>Add document modal</t>
+  </si>
+  <si>
+    <t>Upload Document File</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/documents/{docId}/upload</t>
+  </si>
+  <si>
+    <t>Attach &amp; Upload — sets fileName and done=true (handleFileChosen).</t>
+  </si>
+  <si>
+    <t>Path: id, docId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multipart/form-data:
+file: (binary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "doc-1",
+    "fileName": "aadhaar-front.jpg",
+    "done": true
+  }
+}</t>
+  </si>
+  <si>
+    <t>Attach &amp; Upload button</t>
+  </si>
+  <si>
+    <t>▶ PUT / PATCH / DELETE — Documents &amp; KYC</t>
+  </si>
+  <si>
+    <t>Update Document Row</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/documents/{docId}</t>
+  </si>
+  <si>
+    <t>Edit modal: label + mandatory.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "label": "Aadhaar card — client",
+  "mandatory": true
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "doc-1",
+    "label": "Aadhaar card — client",
+    "mandatory": true
+  }
+}</t>
+  </si>
+  <si>
+    <t>Edit document pencil</t>
+  </si>
+  <si>
+    <t>Toggle Document Done</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/documents/{docId}/done</t>
+  </si>
+  <si>
+    <t>ChecklistCheck toggleDoc(id).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "done": true
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "doc-1",
+    "done": true
+  }
+}</t>
+  </si>
+  <si>
+    <t>Document checklist checkbox</t>
+  </si>
+  <si>
+    <t>Delete Document Row</t>
+  </si>
+  <si>
+    <t>deleteDoc(id).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "doc-3",
+    "deleted": true
+  }
+}</t>
+  </si>
+  <si>
+    <t>Trash delete button</t>
+  </si>
+  <si>
+    <t>PAGE 8: Deal Detail — Notes &amp; RM Flags — File: deal-tabs/NotesRmFlagsTab.jsx</t>
+  </si>
+  <si>
+    <t>Note object keys: title, note, tag (RM note|Flag), tone (blue|amber), alert (boolean for Flag).</t>
+  </si>
+  <si>
+    <t>▶ GET Requests — Notes &amp; RM Flags</t>
+  </si>
+  <si>
+    <t>Get Notes &amp; RM Flags</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/notes</t>
+  </si>
+  <si>
+    <t>List matching INITIAL_NOTES shape.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "items": [
+      {
+        "id": "note-1",
+        "title": "Family dynamics",
+        "note": "Father is the decision maker and the payer.",
+        "tag": "RM note",
+        "tone": "blue",
+        "alert": false
+      },
+      {
+        "id": "note-2",
+        "title": "Preference mismatch",
+        "note": "Client wants a doctor in NCR, parents will consider Punjab.",
+        "tag": "Flag",
+        "tone": "amber",
+        "alert": true
+      }
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>NotesRmFlagsTab list</t>
+  </si>
+  <si>
+    <t>▶ POST Requests — Notes &amp; RM Flags</t>
+  </si>
+  <si>
+    <t>Add Note / Flag</t>
+  </si>
+  <si>
+    <t>Add note form: title, body→note, kind→tag (RM note|Flag). Flag sets tone amber + alert true.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "title": "Family dynamics",
+  "note": "Father is the decision maker and the payer.",
+  "kind": "RM note"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "note-3",
+    "title": "Family dynamics",
+    "note": "Father is the decision maker and the payer.",
+    "tag": "RM note",
+    "tone": "blue",
+    "alert": false
+  }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": false,
+  "message": "Please add a title and note."
+}</t>
+  </si>
+  <si>
+    <t>Add note modal (title, kind, note/body)</t>
+  </si>
+  <si>
+    <t>PAGE 9: Deal Detail — Audit — File: deal-tabs/AuditTab.jsx</t>
+  </si>
+  <si>
+    <t>Immutable log. Row keys: timestamp, actor, action, object, source. FE may mask rows by stage (maskAuditLog).</t>
+  </si>
+  <si>
+    <t>▶ GET Requests — Audit</t>
+  </si>
+  <si>
+    <t>Get Audit Log</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/audit</t>
+  </si>
+  <si>
+    <t>Audit table rows. Optional stage query for progressive reveal like maskAuditLog(currentStage).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path: id
+Query: stage — P0|P1|...|P6 (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "items": [
+      {
+        "timestamp": "28 Jul 09:14",
+        "actor": "Rohit Khanna",
+        "action": "Viewed masked mobile",
+        "object": "Client contact",
+        "source": "CRM Web"
+      },
+      {
+        "timestamp": "26 Jul 17:02",
+        "actor": "Rohit Khanna",
+        "action": "Raised discount request",
+        "object": "Quote v2",
+        "source": "CRM Web"
+      }
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>AuditTab table</t>
+  </si>
+  <si>
+    <t>Export Audit Log</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/audit/export</t>
+  </si>
+  <si>
+    <t>Export log button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binary file download (xlsx/csv)
+OR { "success": true, "data": { "downloadUrl": "https://..." } }</t>
+  </si>
+  <si>
+    <t>TabHeaderButton Export log</t>
+  </si>
+  <si>
+    <t>PAGE 10: Deal Detail — Payments / Contract (P5) — File: deal-tabs/PaymentsTab.jsx</t>
+  </si>
+  <si>
+    <t>Unlocked at P5 (locked overlay before). Consents: title, note, status, done, pending. Payments: date, mode, reference, amount, collectedBy, status, invoice{name,shared,sharedNote}. Contract timeline: tone, title, note, time. Filters: dealFilter, modeFilter.</t>
+  </si>
+  <si>
+    <t>▶ GET Requests — Payments (P5)</t>
+  </si>
+  <si>
+    <t>Get Payments Tab</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/payments</t>
+  </si>
+  <si>
+    <t>Consents + payments list + contractTimeline + totals footnote fields.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path: id
+Query:
+mode — all|UPI|Cheque|Payment link
+scope — deal|all (FE dealFilter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "p5-1",
+    "stageId": "P5",
+    "dealCode": "MML-D-10428",
+    "totals": {
+      "totalIncludingGst": "₹53,100",
+      "collected": "₹35,000",
+      "outstanding": "₹18,100"
+    },
+    "consents": [
+      {
+        "title": "Data privacy notification",
+        "note": "Accepted by the client on 29 Jun, 4:02 PM.",
+        "status": "Accepted",
+        "done": true
+      },
+      {
+        "title": "Marketing consent",
+        "note": "Opted in to WhatsApp and email · opted out of SMS.",
+        "status": "Partial",
+        "done": false,
+        "pending": true
+      }
+    ],
+    "payments": [
+      {
+        "date": "29 Jun 2026",
+        "mode": "UPI",
+        "reference": "MML-R-88213",
+        "amount": "₹15,000",
+        "collectedBy": "Payment link",
+        "status": "Received",
+        "invoice": {
+          "name": "Invoice-MML-R-88213.pdf",
+          "shared": true,
+          "sharedNote": "Sent by Rohit K. · 29 Jun, 4:18 PM"
+        }
+      },
+      {
+        "date": "Due 02 Aug",
+        "mode": "Payment link",
+        "reference": "MML-R-88512",
+        "amount": "₹18,100",
+        "collectedBy": "—",
+        "status": "Awaiting",
+        "invoice": {
+          "name": "Invoice-MML-R-88512.pdf",
+          "shared": false,
+          "sharedNote": "Not shared yet"
+        }
+      }
+    ],
+    "contractTimeline": [
+      {
+        "title": "OTP verified &amp; signed",
+        "note": "OTP sent to +91 98•• •• 4412.",
+        "time": "29 Jun 2026, 6:18 PM — client",
+        "tone": "green"
+      },
+      {
+        "title": "Contract generated from quote v2",
+        "note": "Premium package — ₹53,100 after approved discount and GST.",
+        "time": "29 Jun 2026, 5:40 PM — you",
+        "tone": "green"
+      }
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>PaymentsTab full screen</t>
+  </si>
+  <si>
+    <t>Download Invoice PDF</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/payments/{reference}/invoice</t>
+  </si>
+  <si>
+    <t>Per-row invoice Download (invoice.name).</t>
+  </si>
+  <si>
+    <t>Path: id, reference (e.g. MML-R-88213)</t>
+  </si>
+  <si>
+    <t>Binary PDF download</t>
+  </si>
+  <si>
+    <t>InvoiceCell Download</t>
+  </si>
+  <si>
+    <t>Download Consolidated Invoice</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/payments/invoice-pdf</t>
+  </si>
+  <si>
+    <t>Header Invoice PDF button.</t>
+  </si>
+  <si>
+    <t>OutlineButton Invoice PDF</t>
+  </si>
+  <si>
+    <t>▶ POST / PATCH — Payments (P5)</t>
+  </si>
+  <si>
+    <t>Share / Reshare Invoice</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/payments/{reference}/invoice/share</t>
+  </si>
+  <si>
+    <t>InvoiceCell Send/Reshare — sets invoice.shared true + sharedNote.</t>
+  </si>
+  <si>
+    <t>Path: id, reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "channel": "whatsapp"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "reference": "MML-R-88512",
+    "invoice": {
+      "name": "Invoice-MML-R-88512.pdf",
+      "shared": true,
+      "sharedNote": "Sent &amp; shared by sales · just now"
+    }
+  }
+}</t>
+  </si>
+  <si>
+    <t>InvoiceCell Send / Reshare</t>
+  </si>
+  <si>
+    <t>Toggle Consent Item</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/payments/consents</t>
+  </si>
+  <si>
+    <t>toggleConsent(title) — done + status Accepted|Pending.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "title": "Marketing consent",
+  "done": true
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "title": "Marketing consent",
+    "done": true,
+    "status": "Accepted"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Consent &amp; compliance CheckRow</t>
+  </si>
+  <si>
+    <t>Advance to P6 (from Payments)</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/payments/advance-p6</t>
+  </si>
+  <si>
+    <t>Advance to P6 button. FE blocks while outstanding balance exists. On success stageId becomes P6 (or call existing PATCH stage).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "stageId": "P6",
+    "outstanding": "₹0"
+  }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": false,
+  "message": "P6 stays locked until the balance clears."
+}</t>
+  </si>
+  <si>
+    <t>PrimaryButton Advance to P6</t>
+  </si>
+  <si>
+    <t>Payments note: Payment history button is FE navigate/toast for now. Status values: Received|Cleared|Awaiting. Modes: UPI|Cheque|Payment link.</t>
+  </si>
+  <si>
+    <t>PAGE 11: Deal Detail — Handover to Services (P6) — File: deal-tabs/P6ChecklistTab.jsx</t>
+  </si>
+  <si>
+    <t>Checklist sections (n, heading, items[{title,note,status,done}]). Handover queue rows: deal, client, pkg, verified, verifiedPct, blocking, owner, status. Handover assigns service manager (DealDetailPage DUMMY_MANAGER → serviceAssigned {manager, branch}).</t>
+  </si>
+  <si>
+    <t>▶ GET Requests — P6 Checklist</t>
+  </si>
+  <si>
+    <t>Get P6 Handover Checklist</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/p6</t>
+  </si>
+  <si>
+    <t>Sections + progress + serviceAssigned + queue (optional branch-wide).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path: id
+Query:
+sortMode — blocked|ready
+period — month|quarter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "id": "p6-1",
+    "stageId": "P6",
+    "clientName": "Sanjay Mehta",
+    "doneCount": 13,
+    "totalCount": 16,
+    "percent": 81,
+    "checklistReady": false,
+    "serviceAssigned": null,
+    "sections": [
+      {
+        "n": 1,
+        "heading": "Identity &amp; verification documents",
+        "items": [
+          {
+            "title": "Aadhaar card",
+            "note": "Auto-verified via KYC API on 29 Jun.",
+            "status": "Verified",
+            "done": true
+          },
+          {
+            "title": "Police verification",
+            "note": "Third-party request raised 24 Jul.",
+            "status": "In progress",
+            "done": false
+          }
+        ]
+      },
+      {
+        "n": 4,
+        "heading": "Commercial &amp; consent",
+        "items": [
+          {
+            "title": "Payment cleared in full",
+            "note": "₹18,100 balance outstanding.",
+            "status": "Pending",
+            "done": false
+          },
+          {
+            "title": "Contract signed with OTP",
+            "note": "Signed 29 Jun, 6:18 PM.",
+            "status": "Verified",
+            "done": true
+          }
+        ]
+      }
+    ],
+    "queue": [
+      {
+        "deal": "MML-D-10428",
+        "client": "Sanjay Mehta",
+        "pkg": "Premium",
+        "verified": "13/16",
+        "verifiedPct": 81,
+        "blocking": "Balance payment",
+        "owner": "Rohit Khanna",
+        "status": "Blocked"
+      }
+    ]
+  }
+}</t>
+  </si>
+  <si>
+    <t>P6ChecklistTab</t>
+  </si>
+  <si>
+    <t>▶ POST / PATCH — P6 Checklist</t>
+  </si>
+  <si>
+    <t>Toggle P6 Checklist Item</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/p6/items</t>
+  </si>
+  <si>
+    <t>toggleItem(title) — done + status Verified|Pending.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "title": "Payment cleared in full",
+  "done": true
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "title": "Payment cleared in full",
+    "done": true,
+    "status": "Verified",
+    "doneCount": 14,
+    "totalCount": 16,
+    "percent": 88,
+    "checklistReady": false
+  }
+}</t>
+  </si>
+  <si>
+    <t>P6 CheckRow onToggle</t>
+  </si>
+  <si>
+    <t>Verify All Documents</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/p6/verify-all</t>
+  </si>
+  <si>
+    <t>verifyAll() — marks every checklist item done/Verified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "doneCount": 16,
+    "totalCount": 16,
+    "percent": 100,
+    "checklistReady": true
+  }
+}</t>
+  </si>
+  <si>
+    <t>PrimaryButton Verify all documents</t>
+  </si>
+  <si>
+    <t>Handover to Services</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/p6/handover</t>
+  </si>
+  <si>
+    <t>Handover to services / assign service manager. Returns serviceAssigned {manager, branch} (FE BranchManagerAssignedModal).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "managerId": "u-mgr-1"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": true,
+  "data": {
+    "serviceAssigned": {
+      "manager": "Anita Kapoor",
+      "branch": "Rajouri Garden"
+    },
+    "stageId": "P6",
+    "handedOver": true
+  }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+  "success": false,
+  "message": "Checklist incomplete — handover blocked."
+}</t>
+  </si>
+  <si>
+    <t>Handover to services / Service manager is assigned</t>
+  </si>
+  <si>
+    <t>Download Checklist Template</t>
+  </si>
+  <si>
+    <t>/api/v1/pipeline/leads/{id}/p6/checklist-template</t>
+  </si>
+  <si>
+    <t>Checklist template button download.</t>
+  </si>
+  <si>
+    <t>Binary file download</t>
+  </si>
+  <si>
+    <t>OutlineButton Checklist template</t>
+  </si>
+  <si>
+    <t>P6 note: Queue filters sortMode blocked|ready and period month|quarter are query params on GET. Founder exception release can be a later PATCH — FE footnote only today. Stage moves still use PATCH .../stage where applicable.</t>
+  </si>
+  <si>
+    <t>DOCUMENT COMPLETE — Pipeline deal detail tabs covered</t>
+  </si>
+  <si>
+    <t>Covered pages: 1 Board · 2 Add P0 · 3 Overview · 4 Intake P2 · 5 Visits P3 · 6 Package P4 · 7 Documents · 8 Notes · 9 Audit · 10 Payments P5 · 11 P6 Checklist. Optional later: Cross-branch flags detail page, Calendar CreateTask from deal header, Call logging. Same rules throughout: FE static UI; BE dynamic camelCase fields from frontend.</t>
+  </si>
+  <si>
+    <t>Document version: 2.0  |  Full deal-detail pipeline API set  |  Status: Ready for client / backend review</t>
   </si>
 </sst>
 </file>
@@ -1951,7 +3155,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3F4F6"/>
+        <fgColor rgb="FFE7F8EF"/>
       </patternFill>
     </fill>
   </fills>
@@ -2404,7 +3608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K210"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -4754,53 +5958,2013 @@
       <c r="J108" s="18"/>
       <c r="K108" s="18"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="25" t="s">
+    <row r="111" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="B111" s="25"/>
-      <c r="C111" s="25"/>
-      <c r="D111" s="25"/>
-      <c r="E111" s="25"/>
-      <c r="F111" s="25"/>
-      <c r="G111" s="25"/>
-      <c r="H111" s="25"/>
-      <c r="I111" s="25"/>
-      <c r="J111" s="25"/>
-      <c r="K111" s="25"/>
-    </row>
-    <row r="112" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" s="26" t="s">
+      <c r="B111" s="5"/>
+      <c r="C111" s="5"/>
+      <c r="D111" s="5"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="5"/>
+      <c r="H111" s="5"/>
+      <c r="I111" s="5"/>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
+    </row>
+    <row r="112" ht="48" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="B112" s="26"/>
-      <c r="C112" s="26"/>
-      <c r="D112" s="26"/>
-      <c r="E112" s="26"/>
-      <c r="F112" s="26"/>
-      <c r="G112" s="26"/>
-      <c r="H112" s="26"/>
-      <c r="I112" s="26"/>
-      <c r="J112" s="26"/>
-      <c r="K112" s="26"/>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" s="27" t="s">
+      <c r="B112" s="6"/>
+      <c r="C112" s="6"/>
+      <c r="D112" s="6"/>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
+      <c r="G112" s="6"/>
+      <c r="H112" s="6"/>
+      <c r="I112" s="6"/>
+      <c r="J112" s="6"/>
+      <c r="K112" s="6"/>
+    </row>
+    <row r="114" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="B113" s="27"/>
-      <c r="C113" s="27"/>
-      <c r="D113" s="27"/>
-      <c r="E113" s="27"/>
-      <c r="F113" s="27"/>
-      <c r="G113" s="27"/>
-      <c r="H113" s="27"/>
-      <c r="I113" s="27"/>
-      <c r="J113" s="27"/>
-      <c r="K113" s="27"/>
+      <c r="B114" s="7"/>
+      <c r="C114" s="7"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="7"/>
+      <c r="F114" s="7"/>
+      <c r="G114" s="7"/>
+      <c r="H114" s="7"/>
+      <c r="I114" s="7"/>
+      <c r="J114" s="7"/>
+      <c r="K114" s="7"/>
+    </row>
+    <row r="115" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H115" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J115" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K115" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="116" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" s="9">
+        <v>1</v>
+      </c>
+      <c r="B116" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D116" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G116" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H116" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I116" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="J116" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K116" s="10" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="117" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" s="12">
+        <v>2</v>
+      </c>
+      <c r="B117" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="C117" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D117" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="F117" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G117" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H117" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I117" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="J117" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K117" s="13" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="118" ht="99" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" s="9">
+        <v>3</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D118" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="F118" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G118" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H118" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I118" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="J118" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K118" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="120" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="B120" s="15"/>
+      <c r="C120" s="15"/>
+      <c r="D120" s="15"/>
+      <c r="E120" s="15"/>
+      <c r="F120" s="15"/>
+      <c r="G120" s="15"/>
+      <c r="H120" s="15"/>
+      <c r="I120" s="15"/>
+      <c r="J120" s="15"/>
+      <c r="K120" s="15"/>
+    </row>
+    <row r="121" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H121" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J121" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K121" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="122" ht="88" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" s="9">
+        <v>1</v>
+      </c>
+      <c r="B122" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="C122" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D122" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="F122" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G122" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H122" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="I122" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="J122" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="K122" s="10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="123" ht="132" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" s="12">
+        <v>2</v>
+      </c>
+      <c r="B123" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="C123" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="E123" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="F123" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G123" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H123" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="I123" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="J123" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="K123" s="13" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="124" ht="132" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" s="9">
+        <v>3</v>
+      </c>
+      <c r="B124" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="C124" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D124" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="F124" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G124" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H124" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="I124" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="J124" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="K124" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="125" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" s="12">
+        <v>4</v>
+      </c>
+      <c r="B125" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="C125" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D125" s="13" t="s">
+        <v>316</v>
+      </c>
+      <c r="E125" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="F125" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G125" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H125" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="I125" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="J125" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K125" s="13" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="126" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" s="9">
+        <v>5</v>
+      </c>
+      <c r="B126" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D126" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="F126" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G126" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H126" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="I126" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="J126" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K126" s="10" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="128" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="B128" s="19"/>
+      <c r="C128" s="19"/>
+      <c r="D128" s="19"/>
+      <c r="E128" s="19"/>
+      <c r="F128" s="19"/>
+      <c r="G128" s="19"/>
+      <c r="H128" s="19"/>
+      <c r="I128" s="19"/>
+      <c r="J128" s="19"/>
+      <c r="K128" s="19"/>
+    </row>
+    <row r="129" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H129" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I129" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J129" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K129" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" s="9">
+        <v>1</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="C130" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D130" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="F130" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G130" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H130" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="I130" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="J130" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K130" s="10" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="131" ht="99" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" s="12">
+        <v>2</v>
+      </c>
+      <c r="B131" s="13" t="s">
+        <v>333</v>
+      </c>
+      <c r="C131" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D131" s="13" t="s">
+        <v>334</v>
+      </c>
+      <c r="E131" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="F131" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G131" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="H131" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="I131" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="J131" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K131" s="13" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="132" ht="42" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="B132" s="18"/>
+      <c r="C132" s="18"/>
+      <c r="D132" s="18"/>
+      <c r="E132" s="18"/>
+      <c r="F132" s="18"/>
+      <c r="G132" s="18"/>
+      <c r="H132" s="18"/>
+      <c r="I132" s="18"/>
+      <c r="J132" s="18"/>
+      <c r="K132" s="18"/>
+    </row>
+    <row r="135" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="B135" s="5"/>
+      <c r="C135" s="5"/>
+      <c r="D135" s="5"/>
+      <c r="E135" s="5"/>
+      <c r="F135" s="5"/>
+      <c r="G135" s="5"/>
+      <c r="H135" s="5"/>
+      <c r="I135" s="5"/>
+      <c r="J135" s="5"/>
+      <c r="K135" s="5"/>
+    </row>
+    <row r="136" ht="48" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="B136" s="6"/>
+      <c r="C136" s="6"/>
+      <c r="D136" s="6"/>
+      <c r="E136" s="6"/>
+      <c r="F136" s="6"/>
+      <c r="G136" s="6"/>
+      <c r="H136" s="6"/>
+      <c r="I136" s="6"/>
+      <c r="J136" s="6"/>
+      <c r="K136" s="6"/>
+    </row>
+    <row r="138" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="B138" s="7"/>
+      <c r="C138" s="7"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="7"/>
+      <c r="F138" s="7"/>
+      <c r="G138" s="7"/>
+      <c r="H138" s="7"/>
+      <c r="I138" s="7"/>
+      <c r="J138" s="7"/>
+      <c r="K138" s="7"/>
+    </row>
+    <row r="139" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B139" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H139" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I139" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J139" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K139" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="140" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" s="9">
+        <v>1</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C140" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D140" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G140" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H140" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I140" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="J140" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K140" s="10" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="142" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="B142" s="15"/>
+      <c r="C142" s="15"/>
+      <c r="D142" s="15"/>
+      <c r="E142" s="15"/>
+      <c r="F142" s="15"/>
+      <c r="G142" s="15"/>
+      <c r="H142" s="15"/>
+      <c r="I142" s="15"/>
+      <c r="J142" s="15"/>
+      <c r="K142" s="15"/>
+    </row>
+    <row r="143" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A143" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H143" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I143" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J143" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K143" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" ht="110" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A144" s="9">
+        <v>1</v>
+      </c>
+      <c r="B144" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="C144" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D144" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="E144" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="F144" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G144" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H144" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="I144" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="J144" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="K144" s="10" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="145" ht="88" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145" s="12">
+        <v>2</v>
+      </c>
+      <c r="B145" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="C145" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D145" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="E145" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="F145" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G145" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="H145" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="I145" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="J145" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K145" s="13" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="147" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="B147" s="19"/>
+      <c r="C147" s="19"/>
+      <c r="D147" s="19"/>
+      <c r="E147" s="19"/>
+      <c r="F147" s="19"/>
+      <c r="G147" s="19"/>
+      <c r="H147" s="19"/>
+      <c r="I147" s="19"/>
+      <c r="J147" s="19"/>
+      <c r="K147" s="19"/>
+    </row>
+    <row r="148" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A148" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H148" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I148" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J148" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K148" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="149" ht="88" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149" s="9">
+        <v>1</v>
+      </c>
+      <c r="B149" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="C149" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="E149" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="F149" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G149" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="H149" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="I149" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="J149" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K149" s="10" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="150" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150" s="12">
+        <v>2</v>
+      </c>
+      <c r="B150" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="C150" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D150" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="E150" s="13" t="s">
+        <v>372</v>
+      </c>
+      <c r="F150" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G150" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="H150" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="I150" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="J150" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K150" s="13" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="151" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A151" s="9">
+        <v>3</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="C151" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D151" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="E151" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="F151" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G151" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="H151" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="I151" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="J151" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K151" s="10" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="154" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B154" s="5"/>
+      <c r="C154" s="5"/>
+      <c r="D154" s="5"/>
+      <c r="E154" s="5"/>
+      <c r="F154" s="5"/>
+      <c r="G154" s="5"/>
+      <c r="H154" s="5"/>
+      <c r="I154" s="5"/>
+      <c r="J154" s="5"/>
+      <c r="K154" s="5"/>
+    </row>
+    <row r="155" ht="48" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B155" s="6"/>
+      <c r="C155" s="6"/>
+      <c r="D155" s="6"/>
+      <c r="E155" s="6"/>
+      <c r="F155" s="6"/>
+      <c r="G155" s="6"/>
+      <c r="H155" s="6"/>
+      <c r="I155" s="6"/>
+      <c r="J155" s="6"/>
+      <c r="K155" s="6"/>
+    </row>
+    <row r="157" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="B157" s="7"/>
+      <c r="C157" s="7"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="7"/>
+      <c r="H157" s="7"/>
+      <c r="I157" s="7"/>
+      <c r="J157" s="7"/>
+      <c r="K157" s="7"/>
+    </row>
+    <row r="158" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A158" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B158" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H158" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I158" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J158" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K158" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="159" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A159" s="9">
+        <v>1</v>
+      </c>
+      <c r="B159" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="C159" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D159" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="E159" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="F159" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G159" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H159" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I159" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="J159" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K159" s="10" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="161" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A161" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="B161" s="15"/>
+      <c r="C161" s="15"/>
+      <c r="D161" s="15"/>
+      <c r="E161" s="15"/>
+      <c r="F161" s="15"/>
+      <c r="G161" s="15"/>
+      <c r="H161" s="15"/>
+      <c r="I161" s="15"/>
+      <c r="J161" s="15"/>
+      <c r="K161" s="15"/>
+    </row>
+    <row r="162" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A162" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B162" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E162" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H162" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I162" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J162" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K162" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="163" ht="121" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A163" s="9">
+        <v>1</v>
+      </c>
+      <c r="B163" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="C163" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D163" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="E163" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="F163" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G163" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H163" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="I163" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="J163" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="K163" s="10" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="166" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A166" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="B166" s="5"/>
+      <c r="C166" s="5"/>
+      <c r="D166" s="5"/>
+      <c r="E166" s="5"/>
+      <c r="F166" s="5"/>
+      <c r="G166" s="5"/>
+      <c r="H166" s="5"/>
+      <c r="I166" s="5"/>
+      <c r="J166" s="5"/>
+      <c r="K166" s="5"/>
+    </row>
+    <row r="167" ht="48" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A167" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="B167" s="6"/>
+      <c r="C167" s="6"/>
+      <c r="D167" s="6"/>
+      <c r="E167" s="6"/>
+      <c r="F167" s="6"/>
+      <c r="G167" s="6"/>
+      <c r="H167" s="6"/>
+      <c r="I167" s="6"/>
+      <c r="J167" s="6"/>
+      <c r="K167" s="6"/>
+    </row>
+    <row r="169" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A169" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="B169" s="7"/>
+      <c r="C169" s="7"/>
+      <c r="D169" s="7"/>
+      <c r="E169" s="7"/>
+      <c r="F169" s="7"/>
+      <c r="G169" s="7"/>
+      <c r="H169" s="7"/>
+      <c r="I169" s="7"/>
+      <c r="J169" s="7"/>
+      <c r="K169" s="7"/>
+    </row>
+    <row r="170" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A170" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B170" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E170" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H170" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I170" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J170" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K170" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="171" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A171" s="9">
+        <v>1</v>
+      </c>
+      <c r="B171" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C171" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D171" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="E171" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="F171" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G171" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="H171" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I171" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="J171" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K171" s="10" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="172" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A172" s="12">
+        <v>2</v>
+      </c>
+      <c r="B172" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="C172" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D172" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="E172" s="13" t="s">
+        <v>406</v>
+      </c>
+      <c r="F172" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G172" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H172" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I172" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="J172" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K172" s="13" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="175" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A175" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="B175" s="5"/>
+      <c r="C175" s="5"/>
+      <c r="D175" s="5"/>
+      <c r="E175" s="5"/>
+      <c r="F175" s="5"/>
+      <c r="G175" s="5"/>
+      <c r="H175" s="5"/>
+      <c r="I175" s="5"/>
+      <c r="J175" s="5"/>
+      <c r="K175" s="5"/>
+    </row>
+    <row r="176" ht="48" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A176" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B176" s="6"/>
+      <c r="C176" s="6"/>
+      <c r="D176" s="6"/>
+      <c r="E176" s="6"/>
+      <c r="F176" s="6"/>
+      <c r="G176" s="6"/>
+      <c r="H176" s="6"/>
+      <c r="I176" s="6"/>
+      <c r="J176" s="6"/>
+      <c r="K176" s="6"/>
+    </row>
+    <row r="178" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A178" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B178" s="7"/>
+      <c r="C178" s="7"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="7"/>
+      <c r="F178" s="7"/>
+      <c r="G178" s="7"/>
+      <c r="H178" s="7"/>
+      <c r="I178" s="7"/>
+      <c r="J178" s="7"/>
+      <c r="K178" s="7"/>
+    </row>
+    <row r="179" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A179" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B179" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D179" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H179" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I179" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J179" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K179" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="180" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A180" s="9">
+        <v>1</v>
+      </c>
+      <c r="B180" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="C180" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D180" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="E180" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="F180" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G180" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="H180" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I180" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="J180" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K180" s="10" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="181" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A181" s="12">
+        <v>2</v>
+      </c>
+      <c r="B181" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="C181" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D181" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="E181" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="F181" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G181" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="H181" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I181" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="J181" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K181" s="13" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="182" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A182" s="9">
+        <v>3</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="C182" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D182" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="E182" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="F182" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G182" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H182" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I182" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="J182" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K182" s="10" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="184" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A184" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="B184" s="15"/>
+      <c r="C184" s="15"/>
+      <c r="D184" s="15"/>
+      <c r="E184" s="15"/>
+      <c r="F184" s="15"/>
+      <c r="G184" s="15"/>
+      <c r="H184" s="15"/>
+      <c r="I184" s="15"/>
+      <c r="J184" s="15"/>
+      <c r="K184" s="15"/>
+    </row>
+    <row r="185" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A185" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D185" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H185" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I185" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J185" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K185" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="186" ht="121" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A186" s="9">
+        <v>1</v>
+      </c>
+      <c r="B186" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="C186" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D186" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="E186" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="F186" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G186" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="H186" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="I186" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="J186" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K186" s="10" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="187" ht="88" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A187" s="12">
+        <v>2</v>
+      </c>
+      <c r="B187" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="C187" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D187" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="E187" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="F187" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G187" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H187" s="13" t="s">
+        <v>439</v>
+      </c>
+      <c r="I187" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="J187" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K187" s="13" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="188" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A188" s="9">
+        <v>3</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="C188" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D188" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="E188" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="F188" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G188" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H188" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="I188" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="J188" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="K188" s="10" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="189" ht="28" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A189" s="18" t="s">
+        <v>448</v>
+      </c>
+      <c r="B189" s="18"/>
+      <c r="C189" s="18"/>
+      <c r="D189" s="18"/>
+      <c r="E189" s="18"/>
+      <c r="F189" s="18"/>
+      <c r="G189" s="18"/>
+      <c r="H189" s="18"/>
+      <c r="I189" s="18"/>
+      <c r="J189" s="18"/>
+      <c r="K189" s="18"/>
+    </row>
+    <row r="192" ht="26" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A192" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B192" s="5"/>
+      <c r="C192" s="5"/>
+      <c r="D192" s="5"/>
+      <c r="E192" s="5"/>
+      <c r="F192" s="5"/>
+      <c r="G192" s="5"/>
+      <c r="H192" s="5"/>
+      <c r="I192" s="5"/>
+      <c r="J192" s="5"/>
+      <c r="K192" s="5"/>
+    </row>
+    <row r="193" ht="48" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A193" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="B193" s="6"/>
+      <c r="C193" s="6"/>
+      <c r="D193" s="6"/>
+      <c r="E193" s="6"/>
+      <c r="F193" s="6"/>
+      <c r="G193" s="6"/>
+      <c r="H193" s="6"/>
+      <c r="I193" s="6"/>
+      <c r="J193" s="6"/>
+      <c r="K193" s="6"/>
+    </row>
+    <row r="195" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A195" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="B195" s="7"/>
+      <c r="C195" s="7"/>
+      <c r="D195" s="7"/>
+      <c r="E195" s="7"/>
+      <c r="F195" s="7"/>
+      <c r="G195" s="7"/>
+      <c r="H195" s="7"/>
+      <c r="I195" s="7"/>
+      <c r="J195" s="7"/>
+      <c r="K195" s="7"/>
+    </row>
+    <row r="196" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A196" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B196" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D196" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E196" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F196" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G196" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H196" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I196" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J196" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K196" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="197" ht="170" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A197" s="9">
+        <v>1</v>
+      </c>
+      <c r="B197" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="C197" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D197" s="10" t="s">
+        <v>453</v>
+      </c>
+      <c r="E197" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="F197" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G197" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="H197" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I197" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="J197" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K197" s="10" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="199" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A199" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="B199" s="15"/>
+      <c r="C199" s="15"/>
+      <c r="D199" s="15"/>
+      <c r="E199" s="15"/>
+      <c r="F199" s="15"/>
+      <c r="G199" s="15"/>
+      <c r="H199" s="15"/>
+      <c r="I199" s="15"/>
+      <c r="J199" s="15"/>
+      <c r="K199" s="15"/>
+    </row>
+    <row r="200" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A200" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B200" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C200" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D200" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E200" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F200" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G200" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H200" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I200" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J200" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K200" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="201" ht="132" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A201" s="9">
+        <v>1</v>
+      </c>
+      <c r="B201" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C201" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="D201" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="E201" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="F201" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G201" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H201" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="I201" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="J201" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K201" s="10" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="202" ht="99" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A202" s="12">
+        <v>2</v>
+      </c>
+      <c r="B202" s="13" t="s">
+        <v>465</v>
+      </c>
+      <c r="C202" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D202" s="13" t="s">
+        <v>466</v>
+      </c>
+      <c r="E202" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="F202" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G202" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H202" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="I202" s="13" t="s">
+        <v>468</v>
+      </c>
+      <c r="J202" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K202" s="13" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="203" ht="121" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A203" s="9">
+        <v>3</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="C203" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D203" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="E203" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="F203" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G203" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H203" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="I203" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="J203" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="K203" s="10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="204" ht="85" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A204" s="12">
+        <v>4</v>
+      </c>
+      <c r="B204" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="C204" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D204" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="E204" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="F204" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G204" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H204" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="I204" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="J204" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K204" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="205" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A205" s="18" t="s">
+        <v>482</v>
+      </c>
+      <c r="B205" s="18"/>
+      <c r="C205" s="18"/>
+      <c r="D205" s="18"/>
+      <c r="E205" s="18"/>
+      <c r="F205" s="18"/>
+      <c r="G205" s="18"/>
+      <c r="H205" s="18"/>
+      <c r="I205" s="18"/>
+      <c r="J205" s="18"/>
+      <c r="K205" s="18"/>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A208" s="25" t="s">
+        <v>483</v>
+      </c>
+      <c r="B208" s="25"/>
+      <c r="C208" s="25"/>
+      <c r="D208" s="25"/>
+      <c r="E208" s="25"/>
+      <c r="F208" s="25"/>
+      <c r="G208" s="25"/>
+      <c r="H208" s="25"/>
+      <c r="I208" s="25"/>
+      <c r="J208" s="25"/>
+      <c r="K208" s="25"/>
+    </row>
+    <row r="209" ht="44" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A209" s="26" t="s">
+        <v>484</v>
+      </c>
+      <c r="B209" s="26"/>
+      <c r="C209" s="26"/>
+      <c r="D209" s="26"/>
+      <c r="E209" s="26"/>
+      <c r="F209" s="26"/>
+      <c r="G209" s="26"/>
+      <c r="H209" s="26"/>
+      <c r="I209" s="26"/>
+      <c r="J209" s="26"/>
+      <c r="K209" s="26"/>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A210" s="27" t="s">
+        <v>485</v>
+      </c>
+      <c r="B210" s="27"/>
+      <c r="C210" s="27"/>
+      <c r="D210" s="27"/>
+      <c r="E210" s="27"/>
+      <c r="F210" s="27"/>
+      <c r="G210" s="27"/>
+      <c r="H210" s="27"/>
+      <c r="I210" s="27"/>
+      <c r="J210" s="27"/>
+      <c r="K210" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="63">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
@@ -4835,7 +7999,35 @@
     <mergeCell ref="A108:K108"/>
     <mergeCell ref="A111:K111"/>
     <mergeCell ref="A112:K112"/>
-    <mergeCell ref="A113:K113"/>
+    <mergeCell ref="A114:K114"/>
+    <mergeCell ref="A120:K120"/>
+    <mergeCell ref="A128:K128"/>
+    <mergeCell ref="A132:K132"/>
+    <mergeCell ref="A135:K135"/>
+    <mergeCell ref="A136:K136"/>
+    <mergeCell ref="A138:K138"/>
+    <mergeCell ref="A142:K142"/>
+    <mergeCell ref="A147:K147"/>
+    <mergeCell ref="A154:K154"/>
+    <mergeCell ref="A155:K155"/>
+    <mergeCell ref="A157:K157"/>
+    <mergeCell ref="A161:K161"/>
+    <mergeCell ref="A166:K166"/>
+    <mergeCell ref="A167:K167"/>
+    <mergeCell ref="A169:K169"/>
+    <mergeCell ref="A175:K175"/>
+    <mergeCell ref="A176:K176"/>
+    <mergeCell ref="A178:K178"/>
+    <mergeCell ref="A184:K184"/>
+    <mergeCell ref="A189:K189"/>
+    <mergeCell ref="A192:K192"/>
+    <mergeCell ref="A193:K193"/>
+    <mergeCell ref="A195:K195"/>
+    <mergeCell ref="A199:K199"/>
+    <mergeCell ref="A205:K205"/>
+    <mergeCell ref="A208:K208"/>
+    <mergeCell ref="A209:K209"/>
+    <mergeCell ref="A210:K210"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
